--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488252_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488252_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1119</v>
+        <v>-0.4014</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.14</v>
+        <v>-1.1832</v>
       </c>
       <c r="F2" t="n">
-        <v>1.028</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>-2.2622</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>0.577</v>
+        <v>0.2876</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0161</v>
+        <v>-0.0594</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5931</v>
+        <v>0.3469</v>
       </c>
       <c r="V2" t="n">
         <v>1.5733</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5011</v>
+        <v>-0.6132</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3092</v>
+        <v>-0.1998</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1918</v>
+        <v>-0.4134</v>
       </c>
       <c r="G3" t="n">
         <v>-2.4853</v>
@@ -688,13 +688,13 @@
         <v>2.4087</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4424</v>
+        <v>-0.5546</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2474</v>
+        <v>-0.138</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.195</v>
+        <v>-0.4166</v>
       </c>
       <c r="V3" t="n">
         <v>0.9444</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.4505</v>
+        <v>-1.299</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1413</v>
+        <v>0.2072</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3092</v>
+        <v>-1.5061</v>
       </c>
       <c r="G4" t="n">
         <v>-1.3832</v>
@@ -766,13 +766,13 @@
         <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.197</v>
+        <v>-1.0455</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8754</v>
+        <v>-0.5269</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3216</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0.9444</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5089</v>
+        <v>-1.4843</v>
       </c>
       <c r="E5" t="n">
         <v>-0.9382</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5707</v>
+        <v>-0.5461</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3166</v>
@@ -844,13 +844,13 @@
         <v>0.1853</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4512</v>
+        <v>-0.4265</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3964</v>
+        <v>-0.3718</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7734</v>
+        <v>-2.7521</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1557</v>
+        <v>-1.4023</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6176</v>
+        <v>-1.3498</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.815</v>
+        <v>-0.4984</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9841</v>
+        <v>0.0929</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8309</v>
+        <v>-0.5913</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0337</v>
+        <v>0.4207</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.516</v>
+        <v>0.4207</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5178</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7812</v>
+        <v>-0.9191</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4681</v>
+        <v>-0.3278</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3131</v>
+        <v>-0.5913</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7411</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>2.594</v>
+        <v>1.297</v>
       </c>
       <c r="S6" t="n">
-        <v>0.671</v>
+        <v>-0.439</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4164</v>
+        <v>0.0299</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7454</v>
+        <v>-0.4688</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6294</v>
+        <v>-1.2589</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.315</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.1263</v>
+        <v>-2.9731</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3845</v>
+        <v>-2.3298</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7417</v>
+        <v>-0.6432</v>
       </c>
       <c r="G7" t="n">
         <v>-4.8347</v>
@@ -1000,13 +1000,13 @@
         <v>2.2234</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5151</v>
+        <v>-0.3619</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3109</v>
+        <v>-0.2561</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2042</v>
+        <v>-0.1057</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2669</v>
+        <v>-2.9863</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.794</v>
+        <v>-2.3194</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4729</v>
+        <v>-0.6669</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4984</v>
+        <v>-3.815</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0929</v>
+        <v>-1.9841</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5913</v>
+        <v>-1.8309</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4207</v>
+        <v>-1.0337</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4207</v>
+        <v>-0.516</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.5178</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9191</v>
+        <v>-2.7812</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3278</v>
+        <v>-1.4681</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5913</v>
+        <v>-1.3131</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R8" t="n">
-        <v>1.297</v>
+        <v>2.594</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9538</v>
+        <v>-0.5419</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3619</v>
+        <v>0.2528</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5919</v>
+        <v>-0.7946</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2589</v>
+        <v>0.6294</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2589</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3017</v>
+        <v>-3.6156</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7485</v>
+        <v>-3.1609</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5532</v>
+        <v>-0.4547</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0547</v>
@@ -1156,13 +1156,13 @@
         <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0796</v>
+        <v>-0.3936</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6901</v>
+        <v>-0.1026</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3895</v>
+        <v>-0.291</v>
       </c>
       <c r="V9" t="n">
         <v>0.9444</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9431</v>
+        <v>-4.698</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2016</v>
+        <v>-2.0058</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7414</v>
+        <v>-2.6922</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2918</v>
@@ -1234,13 +1234,13 @@
         <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5777</v>
+        <v>-0.3326</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0124</v>
+        <v>0.1834</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5653</v>
+        <v>-0.5161</v>
       </c>
       <c r="V10" t="n">
         <v>-2.5177</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6582</v>
+        <v>-4.8129</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9396</v>
+        <v>-2.3405</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7187</v>
+        <v>-2.4724</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8876</v>
@@ -1312,13 +1312,13 @@
         <v>1.8529</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2147</v>
+        <v>-1.3694</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0309</v>
+        <v>-0.4318</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1839</v>
+        <v>-0.9376</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6294</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4464</v>
+        <v>-6.9054</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.0606</v>
+        <v>-6.5935</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3857</v>
+        <v>-0.3119</v>
       </c>
       <c r="G12" t="n">
         <v>-4.2233</v>
@@ -1390,13 +1390,13 @@
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2579</v>
+        <v>-0.7169</v>
       </c>
       <c r="T12" t="n">
-        <v>0.822</v>
+        <v>0.2891</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0799</v>
+        <v>-1.006</v>
       </c>
       <c r="V12" t="n">
         <v>0.6289</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-33.0884</v>
+        <v>-32.5413</v>
       </c>
       <c r="E13" t="n">
-        <v>-22.8132</v>
+        <v>-22.2662</v>
       </c>
       <c r="F13" t="n">
         <v>-10.2749</v>
@@ -1468,13 +1468,13 @@
         <v>16.6758</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.441400000000001</v>
+        <v>-5.894299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3614</v>
+        <v>-0.8142999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.08</v>
+        <v>-5.079899999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.2588</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6787</v>
+        <v>6.3016</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5836</v>
+        <v>3.2902</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0951</v>
+        <v>3.0115</v>
       </c>
       <c r="G14" t="n">
-        <v>7.0669</v>
+        <v>2.2851</v>
       </c>
       <c r="H14" t="n">
-        <v>5.7595</v>
+        <v>1.4955</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3074</v>
+        <v>0.7896</v>
       </c>
       <c r="J14" t="n">
-        <v>5.6587</v>
+        <v>0.9238</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9122</v>
+        <v>0.8716</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.0522</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4082</v>
+        <v>1.3613</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.6239</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5609</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9264</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8529</v>
+        <v>1.1117</v>
       </c>
       <c r="S14" t="n">
-        <v>4.6859</v>
+        <v>0.9811</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7047</v>
+        <v>0.4427</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9812</v>
+        <v>0.5384</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.1477</v>
+        <v>3.7766</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0005</v>
+        <v>3.7766</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.1471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>J. RICARDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1047</v>
+        <v>5.9794</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6819</v>
+        <v>0.9716</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4228</v>
+        <v>5.0078</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2851</v>
+        <v>2.8696</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4955</v>
+        <v>1.4826</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7896</v>
+        <v>1.387</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9238</v>
+        <v>1.3686</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8716</v>
+        <v>0.673</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0522</v>
+        <v>0.6956</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3613</v>
+        <v>1.501</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6239</v>
+        <v>0.8096</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.6914</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7411</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1117</v>
+        <v>2.594</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7842</v>
+        <v>1.4074</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8344</v>
+        <v>0.4946</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0503</v>
+        <v>0.9127</v>
       </c>
       <c r="V15" t="n">
-        <v>3.7766</v>
+        <v>1.8877</v>
       </c>
       <c r="W15" t="n">
-        <v>3.7766</v>
+        <v>1.8877</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RICARDO</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1645</v>
+        <v>5.3957</v>
       </c>
       <c r="E16" t="n">
-        <v>0.482</v>
+        <v>1.3479</v>
       </c>
       <c r="F16" t="n">
-        <v>4.6825</v>
+        <v>4.0478</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8696</v>
+        <v>2.4105</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4826</v>
+        <v>1.9481</v>
       </c>
       <c r="I16" t="n">
-        <v>1.387</v>
+        <v>0.4623</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3686</v>
+        <v>1.4317</v>
       </c>
       <c r="K16" t="n">
-        <v>0.673</v>
+        <v>1.3997</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6956</v>
+        <v>0.032</v>
       </c>
       <c r="M16" t="n">
-        <v>1.501</v>
+        <v>0.9788</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8096</v>
+        <v>0.5485</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6914</v>
+        <v>0.4303</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1853</v>
+        <v>1.6676</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R16" t="n">
         <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5924</v>
+        <v>1.0032</v>
       </c>
       <c r="T16" t="n">
-        <v>0.005</v>
+        <v>0.5282</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5874</v>
+        <v>0.475</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8877</v>
+        <v>0.3144</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8877</v>
+        <v>0.3144</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1204</v>
+        <v>5.3148</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8583</v>
+        <v>3.9188</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2621</v>
+        <v>1.396</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4105</v>
+        <v>7.0669</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9481</v>
+        <v>5.7595</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4623</v>
+        <v>1.3074</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4317</v>
+        <v>5.6587</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3997</v>
+        <v>4.9122</v>
       </c>
       <c r="L17" t="n">
-        <v>0.032</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9788</v>
+        <v>1.4082</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5485</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4303</v>
+        <v>0.5609</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6676</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R17" t="n">
-        <v>2.594</v>
+        <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2721</v>
+        <v>2.322</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0386</v>
+        <v>1.0399</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3107</v>
+        <v>1.2821</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3144</v>
+        <v>-3.1477</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3144</v>
+        <v>-0.0005</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-3.1471</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8102</v>
+        <v>3.0553</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4633</v>
+        <v>0.2674</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3469</v>
+        <v>2.7878</v>
       </c>
       <c r="G18" t="n">
         <v>2.9823</v>
@@ -1858,13 +1858,13 @@
         <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>1.254</v>
+        <v>1.4991</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9314</v>
+        <v>0.7356</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3225</v>
+        <v>0.7635</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3144</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0851</v>
+        <v>3.0248</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.34</v>
+        <v>0.2476</v>
       </c>
       <c r="F19" t="n">
-        <v>2.425</v>
+        <v>2.7772</v>
       </c>
       <c r="G19" t="n">
         <v>2.6044</v>
@@ -1936,13 +1936,13 @@
         <v>2.0382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4081</v>
+        <v>0.5316</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1007</v>
+        <v>0.4869</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3074</v>
+        <v>0.0448</v>
       </c>
       <c r="V19" t="n">
         <v>0.63</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4461</v>
+        <v>1.3247</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8214</v>
+        <v>0.5276</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6248</v>
+        <v>0.7971</v>
       </c>
       <c r="G20" t="n">
         <v>0.6784</v>
@@ -2014,13 +2014,13 @@
         <v>0.3706</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3972</v>
+        <v>0.2758</v>
       </c>
       <c r="T20" t="n">
-        <v>0.674</v>
+        <v>0.3802</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2768</v>
+        <v>-0.1045</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.069</v>
+        <v>1.3146</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0235</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0925</v>
+        <v>1.2402</v>
       </c>
       <c r="G21" t="n">
         <v>0.9157</v>
@@ -2092,13 +2092,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4027</v>
+        <v>-0.157</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2932</v>
+        <v>-0.1455</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7634</v>
+        <v>1.2358</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1557</v>
+        <v>-0.9999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9191</v>
+        <v>2.2357</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1372</v>
+        <v>0.1827</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1433</v>
+        <v>-1.8802</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0062</v>
+        <v>2.0629</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7391</v>
+        <v>-0.4412</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2107</v>
+        <v>-1.8512</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5284</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8763</v>
+        <v>0.6239</v>
       </c>
       <c r="N22" t="n">
-        <v>0.354</v>
+        <v>-0.029</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5223</v>
+        <v>0.6529</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1853</v>
+        <v>0.9264</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1117</v>
+        <v>1.8529</v>
       </c>
       <c r="S22" t="n">
-        <v>0.441</v>
+        <v>0.4411</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5099</v>
+        <v>0.3678</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0689</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7462</v>
+        <v>1.1705</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1843</v>
+        <v>0.4781</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5619</v>
+        <v>0.6924</v>
       </c>
       <c r="G23" t="n">
         <v>1.7089</v>
@@ -2248,13 +2248,13 @@
         <v>1.6676</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1306</v>
+        <v>0.2938</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.2266</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0634</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5733</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. PINILLA NUÑEZ</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6221</v>
+        <v>0.7393</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6221</v>
+        <v>-1.2536</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1.993</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6221</v>
+        <v>0.1372</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.1433</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6221</v>
+        <v>-0.0062</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6221</v>
+        <v>-0.7391</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>-0.2107</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6221</v>
+        <v>-0.5284</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>0.8763</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>0.5223</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.4169</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>0.4119</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>J. PINILLA NUÑEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5343</v>
+        <v>0.6221</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4895</v>
+        <v>0.6221</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0238</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1827</v>
+        <v>0.6221</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.8802</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2.0629</v>
+        <v>0.6221</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4412</v>
+        <v>0.6221</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.8512</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1.41</v>
+        <v>0.6221</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6239</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.029</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6529</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2604</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1385</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0561</v>
+        <v>0.2211</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5869</v>
+        <v>0.7827</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6429</v>
+        <v>-0.5616</v>
       </c>
       <c r="G26" t="n">
         <v>1.5891</v>
@@ -2482,13 +2482,13 @@
         <v>1.1117</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2393</v>
+        <v>0.0379</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2189</v>
+        <v>-0.023</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0204</v>
+        <v>0.0609</v>
       </c>
       <c r="V26" t="n">
         <v>-2.5177</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>33.08860000000001</v>
+        <v>35.6997</v>
       </c>
       <c r="E27" t="n">
-        <v>10.2751</v>
+        <v>10.2749</v>
       </c>
       <c r="F27" t="n">
-        <v>22.8136</v>
+        <v>25.4249</v>
       </c>
       <c r="G27" t="n">
         <v>26.0529</v>
@@ -2539,7 +2539,7 @@
         <v>9.211900000000002</v>
       </c>
       <c r="L27" t="n">
-        <v>6.6807</v>
+        <v>6.680699999999999</v>
       </c>
       <c r="M27" t="n">
         <v>10.1603</v>
@@ -2560,19 +2560,19 @@
         <v>18.5288</v>
       </c>
       <c r="S27" t="n">
-        <v>6.4415</v>
+        <v>9.052899999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>5.08</v>
+        <v>5.079900000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3615</v>
+        <v>3.9729</v>
       </c>
       <c r="V27" t="n">
         <v>-1.2588</v>
       </c>
       <c r="W27" t="n">
-        <v>5.978199999999999</v>
+        <v>5.9782</v>
       </c>
       <c r="X27" t="n">
         <v>-7.2369</v>
